--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="72">
   <si>
     <t>Mat</t>
   </si>
@@ -82,18 +82,21 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>MARIANO</t>
   </si>
   <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
     <t>NAMORADO</t>
   </si>
   <si>
@@ -124,99 +130,72 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>ILLESCAS</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
     <t>ROGELIO</t>
   </si>
   <si>
-    <t>JAQUELINE</t>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
   </si>
   <si>
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
+    <t>YAIR</t>
+  </si>
+  <si>
     <t>ADAN</t>
   </si>
   <si>
@@ -229,6 +208,9 @@
     <t>AISHA NAOMI</t>
   </si>
   <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
     <t>LUZ ESTRELLA</t>
   </si>
   <si>
@@ -248,30 +230,6 @@
   </si>
   <si>
     <t>NAOMI</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>REDA ALAN</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
   </si>
   <si>
     <t>JAHEL</t>
@@ -675,16 +633,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -844,7 +805,7 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -995,16 +956,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1118,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1150,16 +1114,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920148</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1173,22 +1137,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920148</v>
+        <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1196,16 +1160,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920237</v>
+        <v>20330051920244</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1225,10 +1189,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1242,16 +1206,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920337</v>
+        <v>20330051920336</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1265,22 +1229,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920157</v>
+        <v>20330051920337</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1288,16 +1252,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920158</v>
+        <v>20330051920157</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1311,16 +1275,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920164</v>
+        <v>20330051920158</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1334,16 +1298,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920174</v>
+        <v>20330051920164</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1357,16 +1321,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920182</v>
+        <v>20330051920168</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1380,16 +1344,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920388</v>
+        <v>20330051920174</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1403,22 +1367,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920286</v>
+        <v>20330051920182</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1426,22 +1390,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920297</v>
+        <v>20330051920388</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1449,16 +1413,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920301</v>
+        <v>20330051920286</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1472,16 +1436,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920312</v>
+        <v>20330051920297</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1495,208 +1459,70 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920138</v>
+        <v>20330051920301</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920139</v>
+        <v>20330051920312</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051650295</v>
+        <v>20330051920354</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920143</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920146</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920150</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920392</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920244</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920354</v>
-      </c>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="74">
   <si>
     <t>Mat</t>
   </si>
@@ -178,6 +178,9 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -229,10 +232,13 @@
     <t>VANESSA</t>
   </si>
   <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
     <t>NAOMI</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,7 +1129,7 @@
         <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,7 +1152,7 @@
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1169,7 +1175,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1192,7 +1198,7 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1215,7 +1221,7 @@
         <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1238,7 +1244,7 @@
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1261,7 +1267,7 @@
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1284,7 +1290,7 @@
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1307,7 +1313,7 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1330,7 +1336,7 @@
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1353,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1376,7 +1382,7 @@
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1399,7 +1405,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1422,7 +1428,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1445,7 +1451,7 @@
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1468,7 +1474,7 @@
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1482,16 +1488,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920312</v>
+        <v>20330051920310</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1514,7 +1520,7 @@
         <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1523,6 +1529,29 @@
         <v>12</v>
       </c>
       <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920312</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="76">
   <si>
     <t>Mat</t>
   </si>
@@ -82,58 +82,61 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>GALICIA</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -175,16 +178,16 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>ROGELIO</t>
+    <t>ALEXIS ISAI</t>
   </si>
   <si>
     <t>JACQUELINE</t>
@@ -233,6 +236,9 @@
   </si>
   <si>
     <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>JAHEL</t>
@@ -808,16 +814,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>53.33</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -965,13 +974,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>53.33</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -1088,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1120,16 +1129,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920148</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1149,10 +1158,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1172,10 +1181,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1195,10 +1204,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1218,10 +1227,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1241,10 +1250,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1264,10 +1273,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1287,10 +1296,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1310,10 +1319,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1333,10 +1342,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1356,10 +1365,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1379,10 +1388,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1402,10 +1411,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1425,10 +1434,10 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1448,10 +1457,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1471,10 +1480,10 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1491,13 +1500,13 @@
         <v>20330051920310</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1511,22 +1520,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920354</v>
+        <v>21330051920143</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1534,24 +1543,47 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
+        <v>20330051920354</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
         <v>20330051920312</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>32</v>
       </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
         <v>14</v>
       </c>
-      <c r="G20">
+      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="82">
   <si>
     <t>Mat</t>
   </si>
@@ -94,12 +94,18 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
@@ -136,9 +142,6 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -148,21 +151,24 @@
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
     <t>VILLALBA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -184,6 +190,9 @@
     <t>SANTOS</t>
   </si>
   <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -199,12 +208,18 @@
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
-    <t>YAIR</t>
-  </si>
-  <si>
     <t>ADAN</t>
   </si>
   <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
@@ -239,6 +254,9 @@
   </si>
   <si>
     <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
   </si>
   <si>
     <t>JAHEL</t>
@@ -840,16 +858,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,16 +884,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>61.9</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -886,16 +910,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.38</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -909,16 +936,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>84.38</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1000,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>88.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1026,16 +1056,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>80.95</v>
+        <v>61.9</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1061,7 +1091,7 @@
         <v>78.38</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1087,7 +1117,7 @@
         <v>84.38</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,10 +1165,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,10 +1188,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1181,10 +1211,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1204,10 +1234,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1221,16 +1251,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1244,16 +1274,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920337</v>
+        <v>20330051920381</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1267,22 +1297,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920157</v>
+        <v>20330051920347</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1290,22 +1320,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920158</v>
+        <v>20330051920349</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1313,16 +1343,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920164</v>
+        <v>20330051920157</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1336,16 +1366,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920168</v>
+        <v>20330051920158</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1359,16 +1389,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920174</v>
+        <v>20330051920164</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1382,16 +1412,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920182</v>
+        <v>20330051920168</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1405,16 +1435,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920388</v>
+        <v>20330051920174</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1428,7 +1458,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920286</v>
+        <v>20330051920182</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1437,13 +1467,13 @@
         <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1451,7 +1481,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920297</v>
+        <v>20330051920388</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
@@ -1460,13 +1490,13 @@
         <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1474,16 +1504,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920301</v>
+        <v>20330051920286</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1497,16 +1527,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920310</v>
+        <v>20330051920297</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1520,70 +1550,139 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920143</v>
+        <v>20330051920301</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920354</v>
+        <v>20330051920310</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
+        <v>21330051920143</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920341</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920354</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
         <v>20330051920312</v>
       </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
         <v>14</v>
       </c>
-      <c r="G21">
+      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="88">
   <si>
     <t>Mat</t>
   </si>
@@ -94,9 +94,45 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -106,42 +142,12 @@
     <t>NAMIGTLE</t>
   </si>
   <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -151,9 +157,42 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>VILLALBA</t>
   </si>
   <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -163,34 +202,7 @@
     <t>MOLOHUA</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
+    <t>PONCE</t>
   </si>
   <si>
     <t>CARRERA</t>
@@ -208,9 +220,48 @@
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
     <t>ADAN</t>
   </si>
   <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
     <t>EDGAR DANIEL</t>
   </si>
   <si>
@@ -220,46 +271,13 @@
     <t>ANGEL ALDAHIR</t>
   </si>
   <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
   </si>
   <si>
     <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
   </si>
   <si>
     <t>NAOMI</t>
@@ -1127,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1165,10 +1183,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1188,10 +1206,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1211,10 +1229,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1234,10 +1252,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1251,22 +1269,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920337</v>
+        <v>20330051920157</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1274,22 +1292,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920381</v>
+        <v>20330051920158</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1297,22 +1315,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920347</v>
+        <v>20330051920168</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1320,22 +1338,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920349</v>
+        <v>20330051920173</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1343,16 +1361,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920157</v>
+        <v>20330051920174</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1366,16 +1384,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920158</v>
+        <v>20330051920182</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1389,16 +1407,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920164</v>
+        <v>20330051920388</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1412,22 +1430,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920168</v>
+        <v>20330051920286</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1435,22 +1453,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920174</v>
+        <v>20330051920297</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1458,22 +1476,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920182</v>
+        <v>20330051920301</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1481,22 +1499,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920388</v>
+        <v>20330051920310</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1504,114 +1522,114 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920286</v>
+        <v>21330051920143</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920297</v>
+        <v>20330051920337</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920301</v>
+        <v>20330051920341</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920310</v>
+        <v>20330051920381</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920143</v>
+        <v>20330051920347</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1619,16 +1637,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920341</v>
+        <v>20330051920349</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1645,13 +1663,13 @@
         <v>20330051920354</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1665,24 +1683,70 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
+        <v>20330051920356</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
         <v>20330051920312</v>
       </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
         <v>14</v>
       </c>
-      <c r="G24">
+      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="93">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
@@ -103,49 +109,52 @@
     <t>HUESCA</t>
   </si>
   <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -166,15 +175,36 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>OSORIO</t>
   </si>
   <si>
@@ -184,30 +214,15 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
@@ -229,18 +244,45 @@
     <t>ALDAIR OMAR</t>
   </si>
   <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
     <t>VANNIA GISELLE</t>
   </si>
   <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>AMERICA MICHELLE</t>
   </si>
   <si>
@@ -251,33 +293,6 @@
   </si>
   <si>
     <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
   </si>
   <si>
     <t>NAOMI</t>
@@ -1145,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1177,16 +1192,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920140</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1200,22 +1215,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920237</v>
+        <v>21330051920141</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1223,22 +1238,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920244</v>
+        <v>21330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1246,16 +1261,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920251</v>
+        <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1269,22 +1284,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920244</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1292,22 +1307,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920158</v>
+        <v>20330051920251</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1315,16 +1330,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920168</v>
+        <v>20330051920157</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1338,16 +1353,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920173</v>
+        <v>20330051920158</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1361,16 +1376,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920174</v>
+        <v>20330051920168</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1384,16 +1399,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920182</v>
+        <v>20330051920174</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1407,16 +1422,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920388</v>
+        <v>20330051920182</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1430,22 +1445,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920286</v>
+        <v>20330051920388</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1453,91 +1468,91 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920297</v>
+        <v>21330051920143</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920301</v>
+        <v>20330051920337</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920310</v>
+        <v>20330051920341</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920143</v>
+        <v>20330051920381</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1545,16 +1560,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920337</v>
+        <v>20330051920347</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1568,16 +1583,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920341</v>
+        <v>20330051920349</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1591,16 +1606,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920381</v>
+        <v>20330051920354</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1614,16 +1629,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920347</v>
+        <v>20330051920356</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1637,22 +1652,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920349</v>
+        <v>20330051920164</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1660,22 +1675,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920354</v>
+        <v>20330051920173</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1683,22 +1698,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920356</v>
+        <v>20330051920286</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1706,22 +1721,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920164</v>
+        <v>20330051920297</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1729,16 +1744,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920312</v>
+        <v>20330051920301</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1747,6 +1762,52 @@
         <v>14</v>
       </c>
       <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920310</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920312</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="98">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -91,6 +94,9 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>MARIANO</t>
   </si>
   <si>
@@ -151,12 +157,18 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -208,15 +220,15 @@
     <t>OSORIO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
     <t>MILKA SARAY</t>
   </si>
   <si>
@@ -224,6 +236,9 @@
   </si>
   <si>
     <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
   </si>
   <si>
     <t>JACQUELINE</t>
@@ -1160,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1192,16 +1207,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1215,16 +1230,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920141</v>
+        <v>21330051920140</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1238,16 +1253,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920145</v>
+        <v>21330051920141</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1261,22 +1276,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>21330051920145</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1284,22 +1299,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920244</v>
+        <v>21330051920147</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1307,16 +1322,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920251</v>
+        <v>20330051920237</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1330,22 +1345,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920157</v>
+        <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1353,22 +1368,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920158</v>
+        <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1376,16 +1391,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920168</v>
+        <v>20330051920157</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1399,16 +1414,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920174</v>
+        <v>20330051920158</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1422,16 +1437,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920182</v>
+        <v>20330051920168</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1445,16 +1460,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920388</v>
+        <v>20330051920174</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1468,68 +1483,68 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920143</v>
+        <v>20330051920182</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920337</v>
+        <v>20330051920388</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920341</v>
+        <v>21330051920143</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1537,16 +1552,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920381</v>
+        <v>20330051920337</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1560,16 +1575,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920347</v>
+        <v>20330051920341</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1583,16 +1598,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920349</v>
+        <v>20330051920381</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1606,16 +1621,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920354</v>
+        <v>20330051920347</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1629,16 +1644,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920356</v>
+        <v>20330051920349</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1652,22 +1667,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920164</v>
+        <v>20330051920354</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1675,22 +1690,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920173</v>
+        <v>20330051920356</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1698,22 +1713,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920286</v>
+        <v>20330051920164</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1721,22 +1736,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920297</v>
+        <v>20330051920173</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1744,16 +1759,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920301</v>
+        <v>20330051920286</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1767,16 +1782,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920310</v>
+        <v>20330051920297</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1790,16 +1805,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920312</v>
+        <v>20330051920301</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1808,6 +1823,52 @@
         <v>14</v>
       </c>
       <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920310</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920312</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="100">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>MARIANO</t>
   </si>
   <si>
@@ -239,6 +242,9 @@
   </si>
   <si>
     <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>JACQUELINE</t>
@@ -1175,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1213,10 +1219,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1236,10 +1242,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1259,10 +1265,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1285,7 +1291,7 @@
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1305,10 +1311,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1322,22 +1328,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920237</v>
+        <v>21330051920382</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1345,7 +1351,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920244</v>
+        <v>20330051920237</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1354,7 +1360,7 @@
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1368,7 +1374,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920251</v>
+        <v>20330051920244</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -1377,7 +1383,7 @@
         <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1391,7 +1397,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920157</v>
+        <v>20330051920251</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1400,13 +1406,13 @@
         <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1414,7 +1420,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920158</v>
+        <v>20330051920157</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -1423,7 +1429,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1437,7 +1443,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920168</v>
+        <v>20330051920158</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1446,7 +1452,7 @@
         <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1460,16 +1466,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920174</v>
+        <v>20330051920168</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1483,16 +1489,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920182</v>
+        <v>20330051920174</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1506,7 +1512,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920388</v>
+        <v>20330051920182</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1515,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1529,7 +1535,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920143</v>
+        <v>20330051920388</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
@@ -1538,21 +1544,21 @@
         <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920337</v>
+        <v>21330051920143</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -1561,13 +1567,13 @@
         <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1575,7 +1581,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920341</v>
+        <v>20330051920337</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -1584,7 +1590,7 @@
         <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1598,16 +1604,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920381</v>
+        <v>20330051920341</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
         <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1621,16 +1627,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920347</v>
+        <v>20330051920381</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
         <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1644,7 +1650,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920349</v>
+        <v>20330051920347</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
@@ -1653,7 +1659,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1667,16 +1673,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920354</v>
+        <v>20330051920349</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1690,16 +1696,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920356</v>
+        <v>20330051920354</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1713,22 +1719,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920164</v>
+        <v>20330051920356</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1736,16 +1742,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920173</v>
+        <v>20330051920164</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1759,7 +1765,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920286</v>
+        <v>20330051920173</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
@@ -1768,13 +1774,13 @@
         <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1782,16 +1788,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920297</v>
+        <v>20330051920286</v>
       </c>
       <c r="B27" t="s">
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1805,16 +1811,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920301</v>
+        <v>20330051920297</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1828,16 +1834,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920310</v>
+        <v>20330051920301</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -1851,16 +1857,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920312</v>
+        <v>20330051920310</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
         <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -1869,6 +1875,29 @@
         <v>14</v>
       </c>
       <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920312</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="104">
   <si>
     <t>Mat</t>
   </si>
@@ -94,135 +94,144 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -241,12 +250,12 @@
     <t>ALEXIS ISAI</t>
   </si>
   <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
     <t>LUIS GUILLERMO</t>
   </si>
   <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
     <t>JACQUELINE</t>
   </si>
   <si>
@@ -256,52 +265,55 @@
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
     <t>DINA BERENICE</t>
   </si>
   <si>
-    <t>ALDAIR OMAR</t>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
   </si>
   <si>
     <t>LUZ ESTRELLA</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
   </si>
   <si>
     <t>AMERICA MICHELLE</t>
@@ -1181,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1219,10 +1231,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1242,10 +1254,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1265,10 +1277,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1291,7 +1303,7 @@
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1305,16 +1317,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920147</v>
+        <v>21330051920382</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1328,22 +1340,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920382</v>
+        <v>20330051920236</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1357,10 +1369,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1380,10 +1392,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1403,10 +1415,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1420,22 +1432,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920157</v>
+        <v>20330051920354</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1443,7 +1455,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920158</v>
+        <v>20330051920168</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1452,7 +1464,7 @@
         <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1466,7 +1478,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920168</v>
+        <v>20330051920182</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -1475,7 +1487,7 @@
         <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1489,91 +1501,91 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920174</v>
+        <v>21330051920143</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920182</v>
+        <v>20330051920241</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920388</v>
+        <v>20330051920337</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920143</v>
+        <v>20330051920341</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1581,16 +1593,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920337</v>
+        <v>20330051920381</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1604,16 +1616,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920341</v>
+        <v>20330051920347</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1627,16 +1639,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920381</v>
+        <v>20330051920349</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1650,16 +1662,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920347</v>
+        <v>20330051920356</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1673,22 +1685,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920349</v>
+        <v>20330051920157</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1696,22 +1708,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920354</v>
+        <v>20330051920158</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1719,22 +1731,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920356</v>
+        <v>20330051920164</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1742,16 +1754,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920164</v>
+        <v>20330051920173</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1765,16 +1777,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1788,22 +1800,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920286</v>
+        <v>20330051920388</v>
       </c>
       <c r="B27" t="s">
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1811,16 +1823,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920297</v>
+        <v>20330051920286</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1834,16 +1846,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920301</v>
+        <v>20330051920297</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -1857,16 +1869,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920310</v>
+        <v>20330051920301</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -1880,16 +1892,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920312</v>
+        <v>20330051920310</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -1898,6 +1910,29 @@
         <v>14</v>
       </c>
       <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920312</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -82,6 +82,33 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -91,33 +118,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -163,6 +163,24 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -172,24 +190,6 @@
     <t>NAJERA</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
     <t>SANTOS</t>
   </si>
   <si>
@@ -238,6 +238,33 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>PEDRO ANGEL</t>
   </si>
   <si>
@@ -245,33 +272,6 @@
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
   <si>
     <t>ANGEL GABRIEL</t>
@@ -1225,13 +1225,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
         <v>73</v>
@@ -1248,13 +1248,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920140</v>
+        <v>21330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
         <v>74</v>
@@ -1271,22 +1271,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920141</v>
+        <v>20330051920236</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
         <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1294,22 +1294,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920145</v>
+        <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
         <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1317,22 +1317,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920382</v>
+        <v>20330051920244</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1340,7 +1340,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920236</v>
+        <v>20330051920251</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1363,13 +1363,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920237</v>
+        <v>20330051920354</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
         <v>79</v>
@@ -1378,7 +1378,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1386,13 +1386,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920244</v>
+        <v>20330051920168</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>80</v>
@@ -1401,7 +1401,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1409,13 +1409,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920251</v>
+        <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
         <v>81</v>
@@ -1424,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1432,30 +1432,30 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920354</v>
+        <v>21330051920135</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
         <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920168</v>
+        <v>21330051920140</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1467,18 +1467,18 @@
         <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920182</v>
+        <v>21330051920141</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -1490,13 +1490,13 @@
         <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1596,7 +1596,7 @@
         <v>20330051920381</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
         <v>61</v>
@@ -1875,7 +1875,7 @@
         <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
         <v>101</v>
@@ -1918,7 +1918,7 @@
         <v>20330051920312</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
         <v>72</v>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,253 +82,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>MARIANO</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>HUESCA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>CALIHUA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>OSORIO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
     <t>JACQUELINE</t>
   </si>
   <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
     <t>ALDAIR OMAR</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
   </si>
 </sst>
 </file>
@@ -1070,16 +857,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>53.33</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1096,16 +883,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1122,16 +909,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>61.9</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1148,16 +935,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>78.38</v>
+        <v>97.3</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1174,16 +961,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1193,7 +980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1225,22 +1012,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>20330051920237</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1248,22 +1035,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920382</v>
+        <v>20330051920251</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1271,22 +1058,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920236</v>
+        <v>20330051920168</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1294,645 +1081,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920244</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920251</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920354</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920168</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920182</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920135</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920140</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920141</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920143</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920241</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920337</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920341</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920381</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920347</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920349</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920356</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920157</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920158</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920164</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920173</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920174</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920388</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920286</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920297</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920301</v>
-      </c>
-      <c r="B30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920310</v>
-      </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" t="s">
-        <v>102</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920312</v>
-      </c>
-      <c r="B32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32">
         <v>1</v>
       </c>
     </row>
